--- a/data/WP17/WP17_sachgebiete_GRÜNE_zeitreihe.xlsx
+++ b/data/WP17/WP17_sachgebiete_GRÜNE_zeitreihe.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t xml:space="preserve">periode</t>
   </si>
@@ -162,9 +162,6 @@
   </si>
   <si>
     <t xml:space="preserve">Öffentliche Vergabe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internationale Beziehungen</t>
   </si>
   <si>
     <t xml:space="preserve">Natur</t>
@@ -1695,16 +1692,16 @@
         <v>3</v>
       </c>
       <c r="D52" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" t="s">
         <v>17</v>
       </c>
-      <c r="E52" t="n">
-        <v>3</v>
-      </c>
-      <c r="F52" t="s">
-        <v>50</v>
-      </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -1724,7 +1721,7 @@
         <v>2</v>
       </c>
       <c r="F53" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G53" t="n">
         <v>2</v>
@@ -1735,7 +1732,7 @@
         <v>44470</v>
       </c>
       <c r="B54" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C54" t="n">
         <v>2</v>
@@ -1787,7 +1784,7 @@
         <v>53</v>
       </c>
       <c r="D56" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E56" t="n">
         <v>2</v>
@@ -1804,7 +1801,7 @@
         <v>44562</v>
       </c>
       <c r="B57" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C57" t="n">
         <v>4</v>
@@ -1839,7 +1836,7 @@
         <v>3</v>
       </c>
       <c r="F58" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G58" t="n">
         <v>2</v>
@@ -1862,7 +1859,7 @@
         <v>3</v>
       </c>
       <c r="F59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G59" t="n">
         <v>2</v>
@@ -1879,7 +1876,7 @@
         <v>5</v>
       </c>
       <c r="D60" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E60" t="n">
         <v>4</v>
@@ -2140,13 +2137,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60DA1E69-7D9F-4FC1-8249-EE8A5EA90045}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A6E15D0-B3ED-4F61-8BF3-76BB6320199F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3A659DE-48F3-4DCD-A319-859533CE3CCC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E3FD650-A242-4B7E-9ADF-DC2637094940}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D918138-AFBF-4306-BC6D-35E7DDDF77E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{146A2818-C582-4ACB-9DF5-F31E4356ACED}"/>
 </file>
--- a/data/WP17/WP17_sachgebiete_GRÜNE_zeitreihe.xlsx
+++ b/data/WP17/WP17_sachgebiete_GRÜNE_zeitreihe.xlsx
@@ -35,12 +35,12 @@
     <t xml:space="preserve">Anzahl_3</t>
   </si>
   <si>
+    <t xml:space="preserve">Innere Sicherheit</t>
+  </si>
+  <si>
     <t xml:space="preserve">Informations- und Kommunikationstechnologien</t>
   </si>
   <si>
-    <t xml:space="preserve">Innere Sicherheit</t>
-  </si>
-  <si>
     <t xml:space="preserve">Datenschutz</t>
   </si>
   <si>
@@ -104,25 +104,25 @@
     <t xml:space="preserve">Sonderpädagogik</t>
   </si>
   <si>
+    <t xml:space="preserve">Kernenergie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umwelt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abfall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fossile Energien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verkehrswegebau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bauwesen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Straßenverkehr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kernenergie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Umwelt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abfall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fossile Energien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verkehrswegebau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bauwesen</t>
   </si>
   <si>
     <t xml:space="preserve">Tier, Tierschutz, Tierhaltung</t>
@@ -539,7 +539,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -562,7 +562,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -582,7 +582,7 @@
         <v>42948</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
@@ -594,7 +594,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
@@ -605,7 +605,7 @@
         <v>42979</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
@@ -663,7 +663,7 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
         <v>3</v>
@@ -697,10 +697,10 @@
         <v>43101</v>
       </c>
       <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="n">
         <v>8</v>
-      </c>
-      <c r="C9" t="n">
-        <v>7</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
@@ -720,7 +720,7 @@
         <v>43132</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
@@ -766,16 +766,16 @@
         <v>43191</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -824,7 +824,7 @@
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
         <v>3</v>
@@ -847,7 +847,7 @@
         <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G15" t="n">
         <v>6</v>
@@ -858,7 +858,7 @@
         <v>43313</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
         <v>2</v>
@@ -904,7 +904,7 @@
         <v>43374</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
         <v>25</v>
@@ -927,7 +927,7 @@
         <v>43405</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
         <v>13</v>
@@ -939,7 +939,7 @@
         <v>13</v>
       </c>
       <c r="F19" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G19" t="n">
         <v>2</v>
@@ -950,16 +950,16 @@
         <v>43435</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
         <v>6</v>
       </c>
       <c r="D20" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
@@ -973,13 +973,13 @@
         <v>43466</v>
       </c>
       <c r="B21" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" t="n">
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
         <v>4</v>
@@ -996,7 +996,7 @@
         <v>43497</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" t="n">
         <v>9</v>
@@ -1008,7 +1008,7 @@
         <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G22" t="n">
         <v>4</v>
@@ -1022,7 +1022,7 @@
         <v>20</v>
       </c>
       <c r="C23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
         <v>12</v>
@@ -1031,7 +1031,7 @@
         <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G23" t="n">
         <v>3</v>
@@ -1048,13 +1048,13 @@
         <v>2</v>
       </c>
       <c r="D24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="s">
         <v>32</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" t="s">
-        <v>33</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1065,7 +1065,7 @@
         <v>43586</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25" t="n">
         <v>46</v>
@@ -1094,7 +1094,7 @@
         <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E26" t="n">
         <v>9</v>
@@ -1111,19 +1111,19 @@
         <v>43647</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
         <v>10</v>
       </c>
       <c r="D27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E27" t="n">
         <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G27" t="n">
         <v>4</v>
@@ -1140,7 +1140,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
@@ -1192,7 +1192,7 @@
         <v>2</v>
       </c>
       <c r="F30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G30" t="n">
         <v>2</v>
@@ -1203,7 +1203,7 @@
         <v>43770</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C31" t="n">
         <v>4</v>
@@ -1249,7 +1249,7 @@
         <v>43831</v>
       </c>
       <c r="B33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33" t="n">
         <v>7</v>
@@ -1301,13 +1301,13 @@
         <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
@@ -1318,7 +1318,7 @@
         <v>43922</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C36" t="n">
         <v>3</v>
@@ -1341,7 +1341,7 @@
         <v>43952</v>
       </c>
       <c r="B37" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C37" t="n">
         <v>8</v>
@@ -1364,7 +1364,7 @@
         <v>43983</v>
       </c>
       <c r="B38" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C38" t="n">
         <v>4</v>
@@ -1410,13 +1410,13 @@
         <v>44044</v>
       </c>
       <c r="B40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40" t="n">
         <v>6</v>
       </c>
       <c r="D40" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E40" t="n">
         <v>3</v>
@@ -1433,7 +1433,7 @@
         <v>44075</v>
       </c>
       <c r="B41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C41" t="n">
         <v>4</v>
@@ -1485,7 +1485,7 @@
         <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
@@ -1525,7 +1525,7 @@
         <v>44197</v>
       </c>
       <c r="B45" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C45" t="n">
         <v>6</v>
@@ -1537,7 +1537,7 @@
         <v>5</v>
       </c>
       <c r="F45" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G45" t="n">
         <v>4</v>
@@ -1548,7 +1548,7 @@
         <v>44228</v>
       </c>
       <c r="B46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C46" t="n">
         <v>7</v>
@@ -1583,7 +1583,7 @@
         <v>3</v>
       </c>
       <c r="F47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G47" t="n">
         <v>3</v>
@@ -1594,7 +1594,7 @@
         <v>44287</v>
       </c>
       <c r="B48" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C48" t="n">
         <v>3</v>
@@ -1646,7 +1646,7 @@
         <v>5</v>
       </c>
       <c r="D50" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E50" t="n">
         <v>4</v>
@@ -1738,13 +1738,13 @@
         <v>2</v>
       </c>
       <c r="D54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E54" t="n">
         <v>2</v>
       </c>
       <c r="F54" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -1755,7 +1755,7 @@
         <v>44501</v>
       </c>
       <c r="B55" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C55" t="n">
         <v>2</v>
@@ -1790,7 +1790,7 @@
         <v>2</v>
       </c>
       <c r="F56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -1807,13 +1807,13 @@
         <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E57" t="n">
         <v>2</v>
       </c>
       <c r="F57" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G57" t="n">
         <v>2</v>
@@ -1824,13 +1824,13 @@
         <v>44593</v>
       </c>
       <c r="B58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C58" t="n">
         <v>9</v>
       </c>
       <c r="D58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E58" t="n">
         <v>3</v>
@@ -1847,13 +1847,13 @@
         <v>44621</v>
       </c>
       <c r="B59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C59" t="n">
         <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E59" t="n">
         <v>3</v>
@@ -2137,13 +2137,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A6E15D0-B3ED-4F61-8BF3-76BB6320199F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF75B17-87F4-479A-954E-01F8E53CA58A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E3FD650-A242-4B7E-9ADF-DC2637094940}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{908445F3-1C01-4440-B0CB-81D2FF909D63}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{146A2818-C582-4ACB-9DF5-F31E4356ACED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC133DC5-52A6-4D80-8A55-B1B0B310AEC9}"/>
 </file>
--- a/data/WP17/WP17_sachgebiete_GRÜNE_zeitreihe.xlsx
+++ b/data/WP17/WP17_sachgebiete_GRÜNE_zeitreihe.xlsx
@@ -2137,13 +2137,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF75B17-87F4-479A-954E-01F8E53CA58A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98C328B7-5463-41C3-B777-F482EEDA5BEA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{908445F3-1C01-4440-B0CB-81D2FF909D63}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EA87CE5-1E23-46C2-AAA2-0AF6084686ED}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC133DC5-52A6-4D80-8A55-B1B0B310AEC9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFF05DD9-B693-484A-AAE2-AE76B3202FAE}"/>
 </file>